--- a/tools/_out/groupB_20261021/out/fs/DesignTable_FS6402_SW2.xlsx
+++ b/tools/_out/groupB_20261021/out/fs/DesignTable_FS6402_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD2"/>
+  <dimension ref="A1:BD8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -880,6 +880,1146 @@
       <c r="BD2" t="inlineStr">
         <is>
           <t>FS6402-08-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FS6402-04-04</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1.344</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.36084</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.1145</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.2165</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.2415</v>
+      </c>
+      <c r="I3" t="n">
+        <v>45</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.23885</v>
+      </c>
+      <c r="L3" t="n">
+        <v>60</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.08301</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.2786</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.03007</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.01389</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.1465</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.2574</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.2796</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.32447</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.21875</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.19169</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.5243</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.1845</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.38338</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.2867</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0.19169</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.21875</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.344</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.989</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>FS6402-04-04</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>ORFS Straight Adapter (male face seal x female JIC swivel), 9/16-18 UN (male O-ring face seal, SAE J1453) x 7/16-20 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>FS6402</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>9/16-18 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>7/16-20 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>[BRENNAN-CAD 2026-10-21 group B: D1@BORE, SNT@DRIVE] [BRENNAN-ONLY 2026-10-18] no Air-Way row -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L@DRIVE: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-04-04 col "L LGTH" = "1.344" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 448.4, page verified True) [Brennan = yes 2026-10-18] - FS face -&gt; JIC swivel nut face (overall); mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); S1HEX@HEX: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-04-04 col "H HEX" = "0.625" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 448.4, page verified True) [Brennan = yes 2026-10-18] - body hex; mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); SHEX@HEX: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-04-04 col "C HEX" = "0.562" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 448.4, page verified True) [Brennan = yes 2026-10-18] - JIC swivel nut hex; mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); THDMAJ_D@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -04 = 0.5625 (PLAN.md s2 FS_THR / the -04 thread of every staged ORFS row); = Brennan "A THREAD" "9/16-18" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_B@DRIVE: end library: straight (UN/UNF) thread of dash -04 = 0.4375 (PLAN.md s2 FS_THR / the -04 thread of every staged ORFS row); = Brennan "B THREAD" "7/16-20" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Thread_D: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-04-04 col "A THREAD" "9/16-18" in the table's format; $PRP@Thread_B: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-04-04 col "B THREAD" "7/16-20" in the table's format; $PRP@TubeOD: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-04-04 col "TUBE O.D." "1/4" in the table's format | MODEL: L face-seal face -&gt; JIC nut face, SNT nut face -&gt; nose tip, body hex S1, nut hex S, bore D1 (Brennan ORFS catalog / CAD record: no Air-Way series; codes placed on the Brennan FS6402-08-08 STEP); male face-seal end = the straight FSM end library; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; one bore D1 from the seal face to the swivel seat; hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-04-04 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>no Air-Way MFS x female JIC swivel series (Air-Way FF6402 is MORB x FFSS = OMi FS6540; Brennan FS6402 only) (Brennan prints it: Brennan-only stays MISSING) | no Air-Way MFS x female JIC swivel series (Air-Way FF6402 is MORB x FFSS = OMi FS6540; Brennan FS6402 only) | OMi parts file row 5556 (no dimensions) | 2026-10-18 Brennan = yes (wave 3 ORFS, staged, not shipped): sizes from Brennan ORFS p5 FS6402-04-04 ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); threads by dash (end library) | Brennan CAD record FS6402-04-04 (PARTcommunity / CADENAS, group B 2026-10-21: D1@BORE=AD, SNT@DRIVE=CC; user 2026-10-21 "yes you can use them following my rule")</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>FS6402-04-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FS6402-06-06</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1.565</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.43301</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="I4" t="n">
+        <v>45</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.27025</v>
+      </c>
+      <c r="L4" t="n">
+        <v>60</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.09701</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.03383</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.3876</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.39722</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.25118</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.2945</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.2925</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.5953000000000001</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.246</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.50236</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.3197</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.25118</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.565</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.3876</v>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>FS6402-06-06</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>ORFS Straight Adapter (male face seal x female JIC swivel), 11/16-16 UN (male O-ring face seal, SAE J1453) x 9/16-18 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>FS6402</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>11/16-16 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>9/16-18 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>[BRENNAN-CAD 2026-10-21 group B: SNT@DRIVE] [BRENNAN-ONLY 2026-10-18] no Air-Way row -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L@DRIVE: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-06-06 col "L LGTH" = "1.565" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 458.4, page verified True) [Brennan = yes 2026-10-18] - FS face -&gt; JIC swivel nut face (overall); mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); S1HEX@HEX: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-06-06 col "H HEX" = "0.750" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 458.4, page verified True) [Brennan = yes 2026-10-18] - body hex; mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); SHEX@HEX: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-06-06 col "C HEX" = "0.688" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 458.4, page verified True) [Brennan = yes 2026-10-18] - JIC swivel nut hex; mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); THDMAJ_D@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -06 = 0.6875 (PLAN.md s2 FS_THR / the -06 thread of every staged ORFS row); = Brennan "A THREAD" "11/16-16" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_B@DRIVE: end library: straight (UN/UNF) thread of dash -06 = 0.5625 (PLAN.md s2 FS_THR / the -06 thread of every staged ORFS row); = Brennan "B THREAD" "9/16-18" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Thread_D: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-06-06 col "A THREAD" "11/16-16" in the table's format; $PRP@Thread_B: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-06-06 col "B THREAD" "9/16-18" in the table's format; $PRP@TubeOD: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-06-06 col "TUBE O.D." "3/8" in the table's format; D1@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: straight ORFS tables: FSM -06 bore on 28 Air-Way row(s) in 8 tables: 0.26 x28 (unanimous) [Air-Way, not Brennan] | MODEL: L face-seal face -&gt; JIC nut face, SNT nut face -&gt; nose tip, body hex S1, nut hex S, bore D1 (Brennan ORFS catalog / CAD record: no Air-Way series; codes placed on the Brennan FS6402-08-08 STEP); male face-seal end = the straight FSM end library; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; one bore D1 from the seal face to the swivel seat; hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-06-06 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>no Air-Way MFS x female JIC swivel series (Air-Way FF6402 is MORB x FFSS = OMi FS6540; Brennan FS6402 only) (Brennan prints it: Brennan-only stays MISSING) | no Air-Way MFS x female JIC swivel series (Air-Way FF6402 is MORB x FFSS = OMi FS6540; Brennan FS6402 only) | OMi parts file row 5557 (no dimensions) | 2026-10-18 Brennan = yes (wave 3 ORFS, staged, not shipped): sizes from Brennan ORFS p5 FS6402-06-06 ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); threads by dash (end library) | Brennan CAD record FS6402-06-06 (PARTcommunity / CADENAS, group B 2026-10-21: SNT@DRIVE=CC; user 2026-10-21 "yes you can use them following my rule")</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>FS6402-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FS6402-10-10</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.61315</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="I5" t="n">
+        <v>45</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="L5" t="n">
+        <v>60</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.448</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.10598</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.03866</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.01786</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.4758</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.4988</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.5265</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.57735</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.39884</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.4475</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.7794</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.394</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.7976799999999999</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.4364</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0.39884</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1.075</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0.5265</v>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>FS6402-10-10</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>ORFS Straight Adapter (male face seal x female JIC swivel), 1-14 UN (male O-ring face seal, SAE J1453) x 7/8-14 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>FS6402</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>1-14 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>7/8-14 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>[BRENNAN-CAD 2026-10-21 group B: D1@BORE, SNT@DRIVE] [BRENNAN-ONLY 2026-10-18] no Air-Way row -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L@DRIVE: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-10-10 col "L LGTH" = "2.060" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 478.6, page verified True) [Brennan = yes 2026-10-18] - FS face -&gt; JIC swivel nut face (overall); mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); S1HEX@HEX: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-10-10 col "H HEX" = "1.062" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 478.6, page verified True) [Brennan = yes 2026-10-18] - body hex; mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); SHEX@HEX: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-10-10 col "C HEX" = "1.000" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 478.6, page verified True) [Brennan = yes 2026-10-18] - JIC swivel nut hex; mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); THDMAJ_D@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -10 = 1.0 (PLAN.md s2 FS_THR / the -10 thread of every staged ORFS row); = Brennan "A THREAD" "1-14" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_B@DRIVE: end library: straight (UN/UNF) thread of dash -10 = 0.875 (PLAN.md s2 FS_THR / the -10 thread of every staged ORFS row); = Brennan "B THREAD" "7/8-14" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Thread_D: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-10-10 col "A THREAD" "1-14" in the table's format; $PRP@Thread_B: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-10-10 col "B THREAD" "7/8-14" in the table's format; $PRP@TubeOD: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-10-10 col "TUBE O.D." "5/8" in the table's format | MODEL: L face-seal face -&gt; JIC nut face, SNT nut face -&gt; nose tip, body hex S1, nut hex S, bore D1 (Brennan ORFS catalog / CAD record: no Air-Way series; codes placed on the Brennan FS6402-08-08 STEP); male face-seal end = the straight FSM end library; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; one bore D1 from the seal face to the swivel seat; hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-10-10 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>no Air-Way MFS x female JIC swivel series (Air-Way FF6402 is MORB x FFSS = OMi FS6540; Brennan FS6402 only) (Brennan prints it: Brennan-only stays MISSING) | no Air-Way MFS x female JIC swivel series (Air-Way FF6402 is MORB x FFSS = OMi FS6540; Brennan FS6402 only) | OMi parts file row 5559 (no dimensions) | 2026-10-18 Brennan = yes (wave 3 ORFS, staged, not shipped): sizes from Brennan ORFS p5 FS6402-10-10 ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); threads by dash (end library) | Brennan CAD record FS6402-10-10 (PARTcommunity / CADENAS, group B 2026-10-21: D1@BORE=AD, SNT@DRIVE=CC; user 2026-10-21 "yes you can use them following my rule")</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>FS6402-10-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FS6402-12-12</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.7216900000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.3385</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.4405</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.5315</v>
+      </c>
+      <c r="I6" t="n">
+        <v>45</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.59375</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.44855</v>
+      </c>
+      <c r="L6" t="n">
+        <v>60</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.5345</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.12499</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.5108</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.089</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.047</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.5928</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.6237</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.5998</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.7216900000000001</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.48614</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.4472</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.549</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.8623</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.4225</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.97228</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.4851</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.48614</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.161</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.5998</v>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>FS6402-12-12</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>ORFS Straight Adapter (male face seal x female JIC swivel), 1 3/16-12 UN (male O-ring face seal, SAE J1453) x 1 1/16-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>FS6402</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>1 3/16-12 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>1 1/16-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>[BRENNAN-CAD 2026-10-21 group B: SNT@DRIVE] [BRENNAN-CAD 2026-10-21: L@DRIVE] [BRENNAN-ONLY 2026-10-18] no Air-Way row -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): S1HEX@HEX: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-12-12 col "H HEX" = "1.250" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 488.7, page verified True) [Brennan = yes 2026-10-18] - body hex; mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); SHEX@HEX: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-12-12 col "C HEX" = "1.250" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 488.7, page verified True) [Brennan = yes 2026-10-18] - JIC swivel nut hex; mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); THDMAJ_D@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -12 = 1.1875 (PLAN.md s2 FS_THR / the -12 thread of every staged ORFS row); = Brennan "A THREAD" "1 3/16-12" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_B@DRIVE: end library: straight (UN/UNF) thread of dash -12 = 1.0625 (PLAN.md s2 FS_THR / the -12 thread of every staged ORFS row); = Brennan "B THREAD" "1 1/16-12" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Thread_D: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-12-12 col "A THREAD" "1 3/16-12" in the table's format; $PRP@Thread_B: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-12-12 col "B THREAD" "1 1/16-12" in the table's format; $PRP@TubeOD: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-12-12 col "TUBE O.D." "3/4" in the table's format; D1@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: straight ORFS tables: FSM -12 bore on 24 Air-Way row(s) in 8 tables: 0.61 x24 (unanimous) [Air-Way, not Brennan] | MODEL: L face-seal face -&gt; JIC nut face, SNT nut face -&gt; nose tip, body hex S1, nut hex S, bore D1 (Brennan ORFS catalog / CAD record: no Air-Way series; codes placed on the Brennan FS6402-08-08 STEP); male face-seal end = the straight FSM end library; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; one bore D1 from the seal face to the swivel seat; hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-12-12 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>no Air-Way MFS x female JIC swivel series (Air-Way FF6402 is MORB x FFSS = OMi FS6540; Brennan FS6402 only) (Brennan prints it: Brennan-only stays MISSING) | no Air-Way MFS x female JIC swivel series (Air-Way FF6402 is MORB x FFSS = OMi FS6540; Brennan FS6402 only) | OMi parts file row 5560 (no dimensions) | 2026-10-18 Brennan = yes (wave 3 ORFS, staged, not shipped): sizes from Brennan ORFS p5 FS6402-12-12 ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); threads by dash (end library) | Brennan CAD record FS6402-12-12 (PARTcommunity / CADENAS, L@DRIVE=L; user 2026-10-21 "yes you can use them following my rule") | Brennan CAD record FS6402-12-12 (PARTcommunity / CADENAS, group B 2026-10-21: SNT@DRIVE=CC; user 2026-10-21 "yes you can use them following my rule")</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>FS6402-12-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FS6402-16-16</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.86603</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.4315</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.5335</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.6565</v>
+      </c>
+      <c r="I7" t="n">
+        <v>45</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.71875</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.46755</v>
+      </c>
+      <c r="L7" t="n">
+        <v>60</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.6595</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.12499</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.4375</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.5298</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.5485</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.139</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.749</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.6564</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.86603</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.61114</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.4873</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.9544</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.5475</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.22228</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.5252</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0.61114</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.855</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.285</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.6564</v>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>FS6402-16-16</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>ORFS Straight Adapter (male face seal x female JIC swivel), 1 7/16-12 UN (male O-ring face seal, SAE J1453) x 1 5/16-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>FS6402</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>1 7/16-12 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>1 5/16-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>[BRENNAN-CAD 2026-10-21 group B: SNT@DRIVE] [BRENNAN-ONLY 2026-10-18] no Air-Way row -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L@DRIVE: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-16-16 col "L LGTH" = "2.460" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 498.8, page verified True) [Brennan = yes 2026-10-18] - FS face -&gt; JIC swivel nut face (overall); mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); S1HEX@HEX: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-16-16 col "H HEX" = "1.500" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 498.8, page verified True) [Brennan = yes 2026-10-18] - body hex; mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); SHEX@HEX: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-16-16 col "C HEX" = "1.500" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 498.8, page verified True) [Brennan = yes 2026-10-18] - JIC swivel nut hex; mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); THDMAJ_D@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -16 = 1.4375 (PLAN.md s2 FS_THR / the -16 thread of every staged ORFS row); = Brennan "A THREAD" "1 7/16-12" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_B@DRIVE: end library: straight (UN/UNF) thread of dash -16 = 1.3125 (PLAN.md s2 FS_THR / the -16 thread of every staged ORFS row); = Brennan "B THREAD" "1 5/16-12" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Thread_D: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-16-16 col "A THREAD" "1 7/16-12" in the table's format; $PRP@Thread_B: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-16-16 col "B THREAD" "1 5/16-12" in the table's format; $PRP@TubeOD: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-16-16 col "TUBE O.D." "1" in the table's format; D1@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: straight ORFS tables: FSM -16 bore on 25 Air-Way row(s) in 8 tables: 0.81 x25 (unanimous) [Air-Way, not Brennan] | MODEL: L face-seal face -&gt; JIC nut face, SNT nut face -&gt; nose tip, body hex S1, nut hex S, bore D1 (Brennan ORFS catalog / CAD record: no Air-Way series; codes placed on the Brennan FS6402-08-08 STEP); male face-seal end = the straight FSM end library; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; one bore D1 from the seal face to the swivel seat; hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-16-16 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>no Air-Way MFS x female JIC swivel series (Air-Way FF6402 is MORB x FFSS = OMi FS6540; Brennan FS6402 only) (Brennan prints it: Brennan-only stays MISSING) | no Air-Way MFS x female JIC swivel series (Air-Way FF6402 is MORB x FFSS = OMi FS6540; Brennan FS6402 only) | OMi parts file row 5561 (no dimensions) | 2026-10-18 Brennan = yes (wave 3 ORFS, staged, not shipped): sizes from Brennan ORFS p5 FS6402-16-16 ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); threads by dash (end library) | Brennan CAD record FS6402-16-16 (PARTcommunity / CADENAS, group B 2026-10-21: SNT@DRIVE=CC; user 2026-10-21 "yes you can use them following my rule")</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>FS6402-16-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FS6402-20-20</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.615</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.01036</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.5565</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.6585</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.7825</v>
+      </c>
+      <c r="I8" t="n">
+        <v>45</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.84375</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.46855</v>
+      </c>
+      <c r="L8" t="n">
+        <v>60</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.7845</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.12499</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.6875</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.5298</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.145</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.9889</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.5375</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.1547</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.76739</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.4345</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.9556</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.766</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.7025</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.53478</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.4724</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0.76739</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>2.615</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.975</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1.355</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0.5375</v>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>FS6402-20-20</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>ORFS Straight Adapter (male face seal x female JIC swivel), 1 11/16-12 UN (male O-ring face seal, SAE J1453) x 1 5/8-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>FS6402</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>1 11/16-12 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>1 5/8-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>[BRENNAN-CAD 2026-10-21 group B: SNT@DRIVE] [BRENNAN-ONLY 2026-10-18] no Air-Way row -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L@DRIVE: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-20-20 col "L LGTH" = "2.615" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 508.8, page verified True) [Brennan = yes 2026-10-18] - FS face -&gt; JIC swivel nut face (overall); mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); S1HEX@HEX: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-20-20 col "H HEX" = "1.750" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 508.8, page verified True) [Brennan = yes 2026-10-18] - body hex; mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); SHEX@HEX: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-20-20 col "C HEX" = "2.000" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 508.8, page verified True) [Brennan = yes 2026-10-18] - JIC swivel nut hex; mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); THDMAJ_D@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -20 = 1.6875 (PLAN.md s2 FS_THR / the -20 thread of every staged ORFS row); = Brennan "A THREAD" "1-11/16-12" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_B@DRIVE: end library: straight (UN/UNF) thread of dash -20 = 1.625 (PLAN.md s2 FS_THR / the -20 thread of every staged ORFS row); = Brennan "B THREAD" "1-5/8-12" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Thread_D: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-20-20 col "A THREAD" "1-11/16-12" in the table's format; $PRP@Thread_B: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-20-20 col "B THREAD" "1-5/8-12" in the table's format; $PRP@TubeOD: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-20-20 col "TUBE O.D." "1 1/4" in the table's format; D1@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: straight ORFS tables: FSM -20 bore on 16 Air-Way row(s) in 8 tables: 1.02 x16 (unanimous) [Air-Way, not Brennan] | MODEL: L face-seal face -&gt; JIC nut face, SNT nut face -&gt; nose tip, body hex S1, nut hex S, bore D1 (Brennan ORFS catalog / CAD record: no Air-Way series; codes placed on the Brennan FS6402-08-08 STEP); male face-seal end = the straight FSM end library; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; one bore D1 from the seal face to the swivel seat; hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-20-20 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>no Air-Way MFS x female JIC swivel series (Air-Way FF6402 is MORB x FFSS = OMi FS6540; Brennan FS6402 only) (Brennan prints it: Brennan-only stays MISSING) | no Air-Way MFS x female JIC swivel series (Air-Way FF6402 is MORB x FFSS = OMi FS6540; Brennan FS6402 only) | OMi parts file row 5562 (no dimensions) | 2026-10-18 Brennan = yes (wave 3 ORFS, staged, not shipped): sizes from Brennan ORFS p5 FS6402-20-20 ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); threads by dash (end library) | Brennan CAD record FS6402-20-20 (PARTcommunity / CADENAS, group B 2026-10-21: SNT@DRIVE=CC; user 2026-10-21 "yes you can use them following my rule")</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>FS6402-20-20</t>
         </is>
       </c>
     </row>

--- a/tools/_out/groupB_20261021/out/fs/DesignTable_FS6402_SW2.xlsx
+++ b/tools/_out/groupB_20261021/out/fs/DesignTable_FS6402_SW2.xlsx
@@ -1059,7 +1059,7 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21 group B: D1@BORE, SNT@DRIVE] [BRENNAN-ONLY 2026-10-18] no Air-Way row -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L@DRIVE: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-04-04 col "L LGTH" = "1.344" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 448.4, page verified True) [Brennan = yes 2026-10-18] - FS face -&gt; JIC swivel nut face (overall); mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); S1HEX@HEX: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-04-04 col "H HEX" = "0.625" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 448.4, page verified True) [Brennan = yes 2026-10-18] - body hex; mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); SHEX@HEX: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-04-04 col "C HEX" = "0.562" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 448.4, page verified True) [Brennan = yes 2026-10-18] - JIC swivel nut hex; mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); THDMAJ_D@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -04 = 0.5625 (PLAN.md s2 FS_THR / the -04 thread of every staged ORFS row); = Brennan "A THREAD" "9/16-18" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_B@DRIVE: end library: straight (UN/UNF) thread of dash -04 = 0.4375 (PLAN.md s2 FS_THR / the -04 thread of every staged ORFS row); = Brennan "B THREAD" "7/16-20" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Thread_D: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-04-04 col "A THREAD" "9/16-18" in the table's format; $PRP@Thread_B: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-04-04 col "B THREAD" "7/16-20" in the table's format; $PRP@TubeOD: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-04-04 col "TUBE O.D." "1/4" in the table's format | MODEL: L face-seal face -&gt; JIC nut face, SNT nut face -&gt; nose tip, body hex S1, nut hex S, bore D1 (Brennan ORFS catalog / CAD record: no Air-Way series; codes placed on the Brennan FS6402-08-08 STEP); male face-seal end = the straight FSM end library; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; one bore D1 from the seal face to the swivel seat; hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-04-04 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>[BRENNAN-CAD 2026-10-21 group B: D1@BORE, SNT@DRIVE] [BRENNAN-ONLY 2026-10-18] no Air-Way row -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L@DRIVE: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-04-04 col "L LGTH" = "1.344" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 448.4, page verified True) [Brennan = yes 2026-10-18] - FS face -&gt; JIC swivel nut face (overall); mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); S1HEX@HEX: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-04-04 col "H HEX" = "0.625" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 448.4, page verified True) [Brennan = yes 2026-10-18] - body hex; mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); SHEX@HEX: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-04-04 col "C HEX" = "0.562" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 448.4, page verified True) [Brennan = yes 2026-10-18] - JIC swivel nut hex; mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); THDMAJ_D@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -04 = 0.5625 (PLAN.md s2 FS_THR / the -04 thread of every staged ORFS row); = Brennan "A THREAD" "9/16-18" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_B@DRIVE: end library: straight (UN/UNF) thread of dash -04 = 0.4375 (PLAN.md s2 FS_THR / the -04 thread of every staged ORFS row); = Brennan "B THREAD" "7/16-20" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Thread_D: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-04-04 col "A THREAD" "9/16-18" in the table's format; $PRP@Thread_B: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-04-04 col "B THREAD" "7/16-20" in the table's format; $PRP@TubeOD: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-04-04 col "TUBE O.D." "1/4" in the table's format | MODEL: L face-seal face -&gt; JIC nut face, SNT nut face -&gt; nose tip, body hex S1, nut hex S, bore D1 (Brennan ORFS catalog / CAD record: no Air-Way series; codes placed on the Brennan FS6402-08-08 STEP); male face-seal end = the straight FSM end library; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; one bore D1 from the seal face to the swivel seat; hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-04-04 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21 group B: SNT@DRIVE] [BRENNAN-ONLY 2026-10-18] no Air-Way row -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L@DRIVE: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-06-06 col "L LGTH" = "1.565" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 458.4, page verified True) [Brennan = yes 2026-10-18] - FS face -&gt; JIC swivel nut face (overall); mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); S1HEX@HEX: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-06-06 col "H HEX" = "0.750" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 458.4, page verified True) [Brennan = yes 2026-10-18] - body hex; mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); SHEX@HEX: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-06-06 col "C HEX" = "0.688" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 458.4, page verified True) [Brennan = yes 2026-10-18] - JIC swivel nut hex; mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); THDMAJ_D@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -06 = 0.6875 (PLAN.md s2 FS_THR / the -06 thread of every staged ORFS row); = Brennan "A THREAD" "11/16-16" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_B@DRIVE: end library: straight (UN/UNF) thread of dash -06 = 0.5625 (PLAN.md s2 FS_THR / the -06 thread of every staged ORFS row); = Brennan "B THREAD" "9/16-18" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Thread_D: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-06-06 col "A THREAD" "11/16-16" in the table's format; $PRP@Thread_B: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-06-06 col "B THREAD" "9/16-18" in the table's format; $PRP@TubeOD: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-06-06 col "TUBE O.D." "3/8" in the table's format; D1@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: straight ORFS tables: FSM -06 bore on 28 Air-Way row(s) in 8 tables: 0.26 x28 (unanimous) [Air-Way, not Brennan] | MODEL: L face-seal face -&gt; JIC nut face, SNT nut face -&gt; nose tip, body hex S1, nut hex S, bore D1 (Brennan ORFS catalog / CAD record: no Air-Way series; codes placed on the Brennan FS6402-08-08 STEP); male face-seal end = the straight FSM end library; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; one bore D1 from the seal face to the swivel seat; hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-06-06 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>[BRENNAN-CAD 2026-10-21 group B: SNT@DRIVE] [BRENNAN-ONLY 2026-10-18] no Air-Way row -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L@DRIVE: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-06-06 col "L LGTH" = "1.565" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 458.4, page verified True) [Brennan = yes 2026-10-18] - FS face -&gt; JIC swivel nut face (overall); mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); S1HEX@HEX: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-06-06 col "H HEX" = "0.750" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 458.4, page verified True) [Brennan = yes 2026-10-18] - body hex; mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); SHEX@HEX: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-06-06 col "C HEX" = "0.688" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 458.4, page verified True) [Brennan = yes 2026-10-18] - JIC swivel nut hex; mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); THDMAJ_D@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -06 = 0.6875 (PLAN.md s2 FS_THR / the -06 thread of every staged ORFS row); = Brennan "A THREAD" "11/16-16" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_B@DRIVE: end library: straight (UN/UNF) thread of dash -06 = 0.5625 (PLAN.md s2 FS_THR / the -06 thread of every staged ORFS row); = Brennan "B THREAD" "9/16-18" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Thread_D: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-06-06 col "A THREAD" "11/16-16" in the table's format; $PRP@Thread_B: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-06-06 col "B THREAD" "9/16-18" in the table's format; $PRP@TubeOD: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-06-06 col "TUBE O.D." "3/8" in the table's format; D1@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: straight ORFS tables: FSM -06 bore on 28 Air-Way row(s) in 8 tables: 0.26 x28 (unanimous) [Air-Way, not Brennan] | MODEL: L face-seal face -&gt; JIC nut face, SNT nut face -&gt; nose tip, body hex S1, nut hex S, bore D1 (Brennan ORFS catalog / CAD record: no Air-Way series; codes placed on the Brennan FS6402-08-08 STEP); male face-seal end = the straight FSM end library; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; one bore D1 from the seal face to the swivel seat; hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-06-06 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21 group B: D1@BORE, SNT@DRIVE] [BRENNAN-ONLY 2026-10-18] no Air-Way row -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L@DRIVE: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-10-10 col "L LGTH" = "2.060" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 478.6, page verified True) [Brennan = yes 2026-10-18] - FS face -&gt; JIC swivel nut face (overall); mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); S1HEX@HEX: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-10-10 col "H HEX" = "1.062" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 478.6, page verified True) [Brennan = yes 2026-10-18] - body hex; mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); SHEX@HEX: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-10-10 col "C HEX" = "1.000" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 478.6, page verified True) [Brennan = yes 2026-10-18] - JIC swivel nut hex; mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); THDMAJ_D@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -10 = 1.0 (PLAN.md s2 FS_THR / the -10 thread of every staged ORFS row); = Brennan "A THREAD" "1-14" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_B@DRIVE: end library: straight (UN/UNF) thread of dash -10 = 0.875 (PLAN.md s2 FS_THR / the -10 thread of every staged ORFS row); = Brennan "B THREAD" "7/8-14" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Thread_D: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-10-10 col "A THREAD" "1-14" in the table's format; $PRP@Thread_B: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-10-10 col "B THREAD" "7/8-14" in the table's format; $PRP@TubeOD: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-10-10 col "TUBE O.D." "5/8" in the table's format | MODEL: L face-seal face -&gt; JIC nut face, SNT nut face -&gt; nose tip, body hex S1, nut hex S, bore D1 (Brennan ORFS catalog / CAD record: no Air-Way series; codes placed on the Brennan FS6402-08-08 STEP); male face-seal end = the straight FSM end library; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; one bore D1 from the seal face to the swivel seat; hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-10-10 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>[BRENNAN-CAD 2026-10-21 group B: D1@BORE, SNT@DRIVE] [BRENNAN-ONLY 2026-10-18] no Air-Way row -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L@DRIVE: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-10-10 col "L LGTH" = "2.060" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 478.6, page verified True) [Brennan = yes 2026-10-18] - FS face -&gt; JIC swivel nut face (overall); mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); S1HEX@HEX: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-10-10 col "H HEX" = "1.062" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 478.6, page verified True) [Brennan = yes 2026-10-18] - body hex; mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); SHEX@HEX: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-10-10 col "C HEX" = "1.000" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 478.6, page verified True) [Brennan = yes 2026-10-18] - JIC swivel nut hex; mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); THDMAJ_D@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -10 = 1.0 (PLAN.md s2 FS_THR / the -10 thread of every staged ORFS row); = Brennan "A THREAD" "1-14" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_B@DRIVE: end library: straight (UN/UNF) thread of dash -10 = 0.875 (PLAN.md s2 FS_THR / the -10 thread of every staged ORFS row); = Brennan "B THREAD" "7/8-14" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Thread_D: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-10-10 col "A THREAD" "1-14" in the table's format; $PRP@Thread_B: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-10-10 col "B THREAD" "7/8-14" in the table's format; $PRP@TubeOD: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-10-10 col "TUBE O.D." "5/8" in the table's format | MODEL: L face-seal face -&gt; JIC nut face, SNT nut face -&gt; nose tip, body hex S1, nut hex S, bore D1 (Brennan ORFS catalog / CAD record: no Air-Way series; codes placed on the Brennan FS6402-08-08 STEP); male face-seal end = the straight FSM end library; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; one bore D1 from the seal face to the swivel seat; hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-10-10 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21 group B: SNT@DRIVE] [BRENNAN-CAD 2026-10-21: L@DRIVE] [BRENNAN-ONLY 2026-10-18] no Air-Way row -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): S1HEX@HEX: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-12-12 col "H HEX" = "1.250" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 488.7, page verified True) [Brennan = yes 2026-10-18] - body hex; mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); SHEX@HEX: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-12-12 col "C HEX" = "1.250" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 488.7, page verified True) [Brennan = yes 2026-10-18] - JIC swivel nut hex; mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); THDMAJ_D@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -12 = 1.1875 (PLAN.md s2 FS_THR / the -12 thread of every staged ORFS row); = Brennan "A THREAD" "1 3/16-12" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_B@DRIVE: end library: straight (UN/UNF) thread of dash -12 = 1.0625 (PLAN.md s2 FS_THR / the -12 thread of every staged ORFS row); = Brennan "B THREAD" "1 1/16-12" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Thread_D: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-12-12 col "A THREAD" "1 3/16-12" in the table's format; $PRP@Thread_B: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-12-12 col "B THREAD" "1 1/16-12" in the table's format; $PRP@TubeOD: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-12-12 col "TUBE O.D." "3/4" in the table's format; D1@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: straight ORFS tables: FSM -12 bore on 24 Air-Way row(s) in 8 tables: 0.61 x24 (unanimous) [Air-Way, not Brennan] | MODEL: L face-seal face -&gt; JIC nut face, SNT nut face -&gt; nose tip, body hex S1, nut hex S, bore D1 (Brennan ORFS catalog / CAD record: no Air-Way series; codes placed on the Brennan FS6402-08-08 STEP); male face-seal end = the straight FSM end library; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; one bore D1 from the seal face to the swivel seat; hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-12-12 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>[BRENNAN-CAD 2026-10-21 group B: SNT@DRIVE] [BRENNAN-CAD 2026-10-21: L@DRIVE] [BRENNAN-ONLY 2026-10-18] no Air-Way row -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): S1HEX@HEX: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-12-12 col "H HEX" = "1.250" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 488.7, page verified True) [Brennan = yes 2026-10-18] - body hex; mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); SHEX@HEX: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-12-12 col "C HEX" = "1.250" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 488.7, page verified True) [Brennan = yes 2026-10-18] - JIC swivel nut hex; mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); THDMAJ_D@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -12 = 1.1875 (PLAN.md s2 FS_THR / the -12 thread of every staged ORFS row); = Brennan "A THREAD" "1 3/16-12" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_B@DRIVE: end library: straight (UN/UNF) thread of dash -12 = 1.0625 (PLAN.md s2 FS_THR / the -12 thread of every staged ORFS row); = Brennan "B THREAD" "1 1/16-12" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Thread_D: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-12-12 col "A THREAD" "1 3/16-12" in the table's format; $PRP@Thread_B: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-12-12 col "B THREAD" "1 1/16-12" in the table's format; $PRP@TubeOD: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-12-12 col "TUBE O.D." "3/4" in the table's format; D1@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: straight ORFS tables: FSM -12 bore on 24 Air-Way row(s) in 8 tables: 0.61 x24 (unanimous) [Air-Way, not Brennan] | MODEL: L face-seal face -&gt; JIC nut face, SNT nut face -&gt; nose tip, body hex S1, nut hex S, bore D1 (Brennan ORFS catalog / CAD record: no Air-Way series; codes placed on the Brennan FS6402-08-08 STEP); male face-seal end = the straight FSM end library; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; one bore D1 from the seal face to the swivel seat; hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-12-12 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21 group B: SNT@DRIVE] [BRENNAN-ONLY 2026-10-18] no Air-Way row -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L@DRIVE: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-16-16 col "L LGTH" = "2.460" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 498.8, page verified True) [Brennan = yes 2026-10-18] - FS face -&gt; JIC swivel nut face (overall); mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); S1HEX@HEX: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-16-16 col "H HEX" = "1.500" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 498.8, page verified True) [Brennan = yes 2026-10-18] - body hex; mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); SHEX@HEX: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-16-16 col "C HEX" = "1.500" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 498.8, page verified True) [Brennan = yes 2026-10-18] - JIC swivel nut hex; mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); THDMAJ_D@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -16 = 1.4375 (PLAN.md s2 FS_THR / the -16 thread of every staged ORFS row); = Brennan "A THREAD" "1 7/16-12" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_B@DRIVE: end library: straight (UN/UNF) thread of dash -16 = 1.3125 (PLAN.md s2 FS_THR / the -16 thread of every staged ORFS row); = Brennan "B THREAD" "1 5/16-12" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Thread_D: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-16-16 col "A THREAD" "1 7/16-12" in the table's format; $PRP@Thread_B: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-16-16 col "B THREAD" "1 5/16-12" in the table's format; $PRP@TubeOD: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-16-16 col "TUBE O.D." "1" in the table's format; D1@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: straight ORFS tables: FSM -16 bore on 25 Air-Way row(s) in 8 tables: 0.81 x25 (unanimous) [Air-Way, not Brennan] | MODEL: L face-seal face -&gt; JIC nut face, SNT nut face -&gt; nose tip, body hex S1, nut hex S, bore D1 (Brennan ORFS catalog / CAD record: no Air-Way series; codes placed on the Brennan FS6402-08-08 STEP); male face-seal end = the straight FSM end library; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; one bore D1 from the seal face to the swivel seat; hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-16-16 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>[BRENNAN-CAD 2026-10-21 group B: SNT@DRIVE] [BRENNAN-ONLY 2026-10-18] no Air-Way row -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L@DRIVE: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-16-16 col "L LGTH" = "2.460" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 498.8, page verified True) [Brennan = yes 2026-10-18] - FS face -&gt; JIC swivel nut face (overall); mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); S1HEX@HEX: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-16-16 col "H HEX" = "1.500" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 498.8, page verified True) [Brennan = yes 2026-10-18] - body hex; mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); SHEX@HEX: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-16-16 col "C HEX" = "1.500" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 498.8, page verified True) [Brennan = yes 2026-10-18] - JIC swivel nut hex; mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); THDMAJ_D@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -16 = 1.4375 (PLAN.md s2 FS_THR / the -16 thread of every staged ORFS row); = Brennan "A THREAD" "1 7/16-12" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_B@DRIVE: end library: straight (UN/UNF) thread of dash -16 = 1.3125 (PLAN.md s2 FS_THR / the -16 thread of every staged ORFS row); = Brennan "B THREAD" "1 5/16-12" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Thread_D: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-16-16 col "A THREAD" "1 7/16-12" in the table's format; $PRP@Thread_B: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-16-16 col "B THREAD" "1 5/16-12" in the table's format; $PRP@TubeOD: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-16-16 col "TUBE O.D." "1" in the table's format; D1@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: straight ORFS tables: FSM -16 bore on 25 Air-Way row(s) in 8 tables: 0.81 x25 (unanimous) [Air-Way, not Brennan] | MODEL: L face-seal face -&gt; JIC nut face, SNT nut face -&gt; nose tip, body hex S1, nut hex S, bore D1 (Brennan ORFS catalog / CAD record: no Air-Way series; codes placed on the Brennan FS6402-08-08 STEP); male face-seal end = the straight FSM end library; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; one bore D1 from the seal face to the swivel seat; hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-16-16 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21 group B: SNT@DRIVE] [BRENNAN-ONLY 2026-10-18] no Air-Way row -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L@DRIVE: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-20-20 col "L LGTH" = "2.615" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 508.8, page verified True) [Brennan = yes 2026-10-18] - FS face -&gt; JIC swivel nut face (overall); mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); S1HEX@HEX: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-20-20 col "H HEX" = "1.750" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 508.8, page verified True) [Brennan = yes 2026-10-18] - body hex; mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); SHEX@HEX: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-20-20 col "C HEX" = "2.000" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 508.8, page verified True) [Brennan = yes 2026-10-18] - JIC swivel nut hex; mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); THDMAJ_D@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -20 = 1.6875 (PLAN.md s2 FS_THR / the -20 thread of every staged ORFS row); = Brennan "A THREAD" "1-11/16-12" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_B@DRIVE: end library: straight (UN/UNF) thread of dash -20 = 1.625 (PLAN.md s2 FS_THR / the -20 thread of every staged ORFS row); = Brennan "B THREAD" "1-5/8-12" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Thread_D: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-20-20 col "A THREAD" "1-11/16-12" in the table's format; $PRP@Thread_B: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-20-20 col "B THREAD" "1-5/8-12" in the table's format; $PRP@TubeOD: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-20-20 col "TUBE O.D." "1 1/4" in the table's format; D1@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: straight ORFS tables: FSM -20 bore on 16 Air-Way row(s) in 8 tables: 1.02 x16 (unanimous) [Air-Way, not Brennan] | MODEL: L face-seal face -&gt; JIC nut face, SNT nut face -&gt; nose tip, body hex S1, nut hex S, bore D1 (Brennan ORFS catalog / CAD record: no Air-Way series; codes placed on the Brennan FS6402-08-08 STEP); male face-seal end = the straight FSM end library; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; one bore D1 from the seal face to the swivel seat; hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-20-20 (both ends; fsmeasure.measure_fsm, group B 2026-10-21); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+          <t>[BRENNAN-CAD 2026-10-21 group B: SNT@DRIVE] [BRENNAN-ONLY 2026-10-18] no Air-Way row -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L@DRIVE: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-20-20 col "L LGTH" = "2.615" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 508.8, page verified True) [Brennan = yes 2026-10-18] - FS face -&gt; JIC swivel nut face (overall); mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); S1HEX@HEX: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-20-20 col "H HEX" = "1.750" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 508.8, page verified True) [Brennan = yes 2026-10-18] - body hex; mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); SHEX@HEX: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-20-20 col "C HEX" = "2.000" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 508.8, page verified True) [Brennan = yes 2026-10-18] - JIC swivel nut hex; mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); THDMAJ_D@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -20 = 1.6875 (PLAN.md s2 FS_THR / the -20 thread of every staged ORFS row); = Brennan "A THREAD" "1-11/16-12" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_B@DRIVE: end library: straight (UN/UNF) thread of dash -20 = 1.625 (PLAN.md s2 FS_THR / the -20 thread of every staged ORFS row); = Brennan "B THREAD" "1-5/8-12" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Thread_D: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-20-20 col "A THREAD" "1-11/16-12" in the table's format; $PRP@Thread_B: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-20-20 col "B THREAD" "1-5/8-12" in the table's format; $PRP@TubeOD: Brennan ORFS catalog p5 table ORFS-p005-t04 "FS6402 MFS-FJS STRAIGHT" row FS6402-20-20 col "TUBE O.D." "1 1/4" in the table's format; D1@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: straight ORFS tables: FSM -20 bore on 16 Air-Way row(s) in 8 tables: 1.02 x16 (unanimous) [Air-Way, not Brennan] | MODEL: L face-seal face -&gt; JIC nut face, SNT nut face -&gt; nose tip, body hex S1, nut hex S, bore D1 (Brennan ORFS catalog / CAD record: no Air-Way series; codes placed on the Brennan FS6402-08-08 STEP); male face-seal end = the straight FSM end library; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; one bore D1 from the seal face to the swivel seat; hex end chamfers NOT modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-20-20 (both ends; fsmeasure.measure_fsm, fsends_20261021); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
